--- a/3_CGE/Game_theory_2024/4_DB/List_producers.xlsx
+++ b/3_CGE/Game_theory_2024/4_DB/List_producers.xlsx
@@ -1,26 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\runGTAP375\Game_theory_2024\4_DB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03D83823-8C03-40DA-9940-49EB1C1E312D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC044094-D29F-4492-AF68-5C8CEF3B193F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31350" yWindow="4245" windowWidth="14400" windowHeight="7365" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-21710" yWindow="-21710" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="46">
   <si>
     <t>Country</t>
   </si>
@@ -28,9 +41,6 @@
     <t>tag</t>
   </si>
   <si>
-    <t>angdrc</t>
-  </si>
-  <si>
     <t>producer</t>
   </si>
   <si>
@@ -130,9 +140,6 @@
     <t>southasia</t>
   </si>
   <si>
-    <t>ssa</t>
-  </si>
-  <si>
     <t>uk</t>
   </si>
   <si>
@@ -143,6 +150,27 @@
   </si>
   <si>
     <t>venezuela</t>
+  </si>
+  <si>
+    <t>angola</t>
+  </si>
+  <si>
+    <t>drc</t>
+  </si>
+  <si>
+    <t>wafr</t>
+  </si>
+  <si>
+    <t>cafr</t>
+  </si>
+  <si>
+    <t>safr</t>
+  </si>
+  <si>
+    <t>eafr</t>
+  </si>
+  <si>
+    <t>nafr</t>
   </si>
 </sst>
 </file>
@@ -186,10 +214,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -495,10 +529,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B38"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:E44"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -506,301 +540,391 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>2</v>
+        <v>39</v>
       </c>
       <c r="B2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="1"/>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="1"/>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
+      <c r="B4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D4" s="1"/>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
         <v>4</v>
       </c>
-      <c r="B3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
+      <c r="B5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D5" s="1"/>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
         <v>5</v>
       </c>
-      <c r="B4" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
+      <c r="B6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D6" s="1"/>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
         <v>6</v>
       </c>
-      <c r="B5" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" t="s">
+      <c r="B7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" s="1"/>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
+      <c r="B8" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="1"/>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
         <v>9</v>
       </c>
-      <c r="B7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
+      <c r="B9" t="s">
+        <v>2</v>
+      </c>
+      <c r="D9" s="1"/>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
         <v>10</v>
       </c>
-      <c r="B8" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
+      <c r="B10" t="s">
+        <v>7</v>
+      </c>
+      <c r="D10" s="1"/>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
         <v>11</v>
       </c>
-      <c r="B9" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
+      <c r="B11" t="s">
+        <v>7</v>
+      </c>
+      <c r="D11" s="1"/>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
         <v>12</v>
       </c>
-      <c r="B10" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
+      <c r="B12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D12" s="1"/>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
         <v>13</v>
       </c>
-      <c r="B11" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
+      <c r="B13" t="s">
+        <v>2</v>
+      </c>
+      <c r="D13" s="1"/>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
         <v>14</v>
       </c>
-      <c r="B12" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
+      <c r="B14" t="s">
+        <v>7</v>
+      </c>
+      <c r="D14" s="1"/>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
         <v>15</v>
       </c>
-      <c r="B13" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
+      <c r="B15" t="s">
+        <v>2</v>
+      </c>
+      <c r="D15" s="1"/>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
         <v>16</v>
       </c>
-      <c r="B14" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
+      <c r="B16" t="s">
+        <v>2</v>
+      </c>
+      <c r="D16" s="1"/>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
         <v>17</v>
       </c>
-      <c r="B15" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
+      <c r="B17" t="s">
+        <v>7</v>
+      </c>
+      <c r="D17" s="1"/>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
         <v>18</v>
       </c>
-      <c r="B16" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
+      <c r="B18" t="s">
+        <v>7</v>
+      </c>
+      <c r="D18" s="1"/>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
         <v>19</v>
       </c>
-      <c r="B17" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A18" t="s">
+      <c r="B19" t="s">
+        <v>7</v>
+      </c>
+      <c r="D19" s="1"/>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
         <v>20</v>
       </c>
-      <c r="B18" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A19" t="s">
+      <c r="B20" t="s">
+        <v>7</v>
+      </c>
+      <c r="D20" s="1"/>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
         <v>21</v>
       </c>
-      <c r="B19" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A20" t="s">
+      <c r="B21" t="s">
+        <v>2</v>
+      </c>
+      <c r="D21" s="1"/>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
         <v>22</v>
       </c>
-      <c r="B20" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A21" t="s">
+      <c r="B22" t="s">
+        <v>7</v>
+      </c>
+      <c r="D22" s="1"/>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
         <v>23</v>
       </c>
-      <c r="B21" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A22" t="s">
+      <c r="B23" t="s">
+        <v>7</v>
+      </c>
+      <c r="D23" s="1"/>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
         <v>24</v>
       </c>
-      <c r="B22" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A23" t="s">
+      <c r="B24" t="s">
+        <v>7</v>
+      </c>
+      <c r="D24" s="1"/>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
         <v>25</v>
       </c>
-      <c r="B23" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A24" t="s">
+      <c r="B25" t="s">
+        <v>7</v>
+      </c>
+      <c r="D25" s="1"/>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
         <v>26</v>
       </c>
-      <c r="B24" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A25" t="s">
+      <c r="B26" t="s">
+        <v>7</v>
+      </c>
+      <c r="D26" s="1"/>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
         <v>27</v>
       </c>
-      <c r="B25" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A26" t="s">
+      <c r="B27" t="s">
+        <v>7</v>
+      </c>
+      <c r="D27" s="1"/>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
         <v>28</v>
       </c>
-      <c r="B26" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A27" t="s">
+      <c r="B28" t="s">
+        <v>7</v>
+      </c>
+      <c r="D28" s="1"/>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
         <v>29</v>
       </c>
-      <c r="B27" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A28" t="s">
+      <c r="B29" t="s">
+        <v>2</v>
+      </c>
+      <c r="D29" s="1"/>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
         <v>30</v>
       </c>
-      <c r="B28" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A29" t="s">
+      <c r="B30" t="s">
+        <v>2</v>
+      </c>
+      <c r="D30" s="1"/>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
         <v>31</v>
       </c>
-      <c r="B29" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A30" t="s">
+      <c r="B31" t="s">
+        <v>7</v>
+      </c>
+      <c r="D31" s="1"/>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
         <v>32</v>
       </c>
-      <c r="B30" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A31" t="s">
+      <c r="B32" t="s">
+        <v>7</v>
+      </c>
+      <c r="D32" s="1"/>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
         <v>33</v>
       </c>
-      <c r="B31" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A32" t="s">
+      <c r="B33" t="s">
+        <v>7</v>
+      </c>
+      <c r="D33" s="1"/>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
         <v>34</v>
       </c>
-      <c r="B32" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A33" t="s">
+      <c r="B34" t="s">
+        <v>7</v>
+      </c>
+      <c r="D34" s="1"/>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A35" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B35" t="s">
+        <v>7</v>
+      </c>
+      <c r="D35" s="1"/>
+      <c r="E35" s="2"/>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A36" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B36" t="s">
+        <v>7</v>
+      </c>
+      <c r="D36" s="1"/>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A37" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B37" t="s">
+        <v>7</v>
+      </c>
+      <c r="D37" s="1"/>
+      <c r="E37" s="2"/>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A38" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B38" t="s">
+        <v>7</v>
+      </c>
+      <c r="D38" s="1"/>
+      <c r="E38" s="2"/>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A39" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B39" t="s">
+        <v>7</v>
+      </c>
+      <c r="D39" s="1"/>
+      <c r="E39" s="2"/>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
         <v>35</v>
       </c>
-      <c r="B33" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A34" t="s">
+      <c r="B40" t="s">
+        <v>7</v>
+      </c>
+      <c r="D40" s="1"/>
+      <c r="E40" s="2"/>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
         <v>36</v>
       </c>
-      <c r="B34" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A35" t="s">
+      <c r="B41" t="s">
+        <v>7</v>
+      </c>
+      <c r="D41" s="1"/>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
         <v>37</v>
       </c>
-      <c r="B35" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A36" t="s">
+      <c r="B42" t="s">
+        <v>7</v>
+      </c>
+      <c r="D42" s="1"/>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
         <v>38</v>
       </c>
-      <c r="B36" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A37" t="s">
-        <v>39</v>
-      </c>
-      <c r="B37" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A38" t="s">
-        <v>40</v>
-      </c>
-      <c r="B38" t="s">
-        <v>8</v>
-      </c>
+      <c r="B43" t="s">
+        <v>7</v>
+      </c>
+      <c r="D43" s="1"/>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D44" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
